--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9664,6 +9664,36 @@
       <c r="H308" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>317.07</v>
+      </c>
+      <c r="C309" t="n">
+        <v>330.09</v>
+      </c>
+      <c r="D309" t="n">
+        <v>362.17</v>
+      </c>
+      <c r="E309" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="F309" t="n">
+        <v>361.36</v>
+      </c>
+      <c r="G309" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B349"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13171,6 +13201,16 @@
       </c>
       <c r="B349" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -13339,28 +13379,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5384569793625325</v>
+        <v>0.5345054321780466</v>
       </c>
       <c r="J2" t="n">
+        <v>308</v>
+      </c>
+      <c r="K2" t="n">
         <v>307</v>
       </c>
-      <c r="K2" t="n">
-        <v>306</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.09127007607176096</v>
+        <v>0.09054801848868754</v>
       </c>
       <c r="M2" t="n">
-        <v>9.797472677779968</v>
+        <v>9.780701595329484</v>
       </c>
       <c r="N2" t="n">
-        <v>150.8522022100355</v>
+        <v>150.4809607115913</v>
       </c>
       <c r="O2" t="n">
-        <v>12.28219044837017</v>
+        <v>12.26706813837729</v>
       </c>
       <c r="P2" t="n">
-        <v>308.9739515936922</v>
+        <v>309.0170890068647</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13421,28 +13461,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6243387257476326</v>
+        <v>0.6184961892204602</v>
       </c>
       <c r="J3" t="n">
+        <v>308</v>
+      </c>
+      <c r="K3" t="n">
         <v>307</v>
       </c>
-      <c r="K3" t="n">
-        <v>306</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2534934111094902</v>
+        <v>0.2504037177783959</v>
       </c>
       <c r="M3" t="n">
-        <v>5.67297408096247</v>
+        <v>5.683371880979616</v>
       </c>
       <c r="N3" t="n">
-        <v>59.98611472494039</v>
+        <v>60.05334370735839</v>
       </c>
       <c r="O3" t="n">
-        <v>7.7450703499026</v>
+        <v>7.749409248927198</v>
       </c>
       <c r="P3" t="n">
-        <v>322.6488909741159</v>
+        <v>322.7126715391405</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13499,28 +13539,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5411738815840564</v>
+        <v>0.5389832783312344</v>
       </c>
       <c r="J4" t="n">
+        <v>308</v>
+      </c>
+      <c r="K4" t="n">
         <v>307</v>
       </c>
-      <c r="K4" t="n">
-        <v>306</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2809468669669396</v>
+        <v>0.2804896836583372</v>
       </c>
       <c r="M4" t="n">
-        <v>4.489974035294534</v>
+        <v>4.488148785241587</v>
       </c>
       <c r="N4" t="n">
-        <v>39.17000822722226</v>
+        <v>39.07933832334271</v>
       </c>
       <c r="O4" t="n">
-        <v>6.258594748601499</v>
+        <v>6.25134692073178</v>
       </c>
       <c r="P4" t="n">
-        <v>351.2856704620951</v>
+        <v>351.3095843756085</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13577,28 +13617,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4231869726368563</v>
+        <v>0.419900745355744</v>
       </c>
       <c r="J5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K5" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1955134727736106</v>
+        <v>0.1937941417333122</v>
       </c>
       <c r="M5" t="n">
-        <v>4.883428549605314</v>
+        <v>4.884318455436333</v>
       </c>
       <c r="N5" t="n">
-        <v>38.45768235990429</v>
+        <v>38.41504517277978</v>
       </c>
       <c r="O5" t="n">
-        <v>6.201425832814925</v>
+        <v>6.19798718720681</v>
       </c>
       <c r="P5" t="n">
-        <v>361.9164707531449</v>
+        <v>361.9524145011451</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13655,28 +13695,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1669492763919506</v>
+        <v>0.1691149759864079</v>
       </c>
       <c r="J6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K6" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07963707071815307</v>
+        <v>0.08189505062214508</v>
       </c>
       <c r="M6" t="n">
-        <v>3.296095654895206</v>
+        <v>3.294759847773883</v>
       </c>
       <c r="N6" t="n">
-        <v>16.81083809203578</v>
+        <v>16.79196658925409</v>
       </c>
       <c r="O6" t="n">
-        <v>4.10010220507194</v>
+        <v>4.097800213438192</v>
       </c>
       <c r="P6" t="n">
-        <v>353.615225498801</v>
+        <v>353.5915377396146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13733,28 +13773,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2081918534267901</v>
+        <v>0.2068028791751728</v>
       </c>
       <c r="J7" t="n">
+        <v>308</v>
+      </c>
+      <c r="K7" t="n">
         <v>307</v>
       </c>
-      <c r="K7" t="n">
-        <v>306</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.06680191657007484</v>
+        <v>0.06636299116871802</v>
       </c>
       <c r="M7" t="n">
-        <v>4.694297507308094</v>
+        <v>4.685078626166417</v>
       </c>
       <c r="N7" t="n">
-        <v>31.5091206057364</v>
+        <v>31.42126012096189</v>
       </c>
       <c r="O7" t="n">
-        <v>5.61329854949266</v>
+        <v>5.60546698509249</v>
       </c>
       <c r="P7" t="n">
-        <v>359.6136258827711</v>
+        <v>359.6288321676293</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13792,7 +13832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26699,6 +26739,48 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-35.122793086454685,173.97984574007546</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-35.122956127891435,173.98074815988667</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-35.122888379356475,173.98171470148282</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-35.122868749598055,173.98261482088762</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-35.122934078647866,173.98351199964532</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-35.12291966412933,173.98441026956272</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9692,6 +9692,66 @@
         <v>362.96</v>
       </c>
       <c r="H309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="C310" t="n">
+        <v>325.22</v>
+      </c>
+      <c r="D310" t="n">
+        <v>360.13</v>
+      </c>
+      <c r="E310" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="F310" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="G310" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>311.92</v>
+      </c>
+      <c r="C311" t="n">
+        <v>326</v>
+      </c>
+      <c r="D311" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="E311" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="F311" t="n">
+        <v>359.23</v>
+      </c>
+      <c r="G311" t="n">
+        <v>364.31</v>
+      </c>
+      <c r="H311" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9708,7 +9768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B350"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13211,6 +13271,26 @@
       </c>
       <c r="B350" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -13379,28 +13459,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5345054321780466</v>
+        <v>0.5200744321937278</v>
       </c>
       <c r="J2" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09054801848868754</v>
+        <v>0.08679103866615845</v>
       </c>
       <c r="M2" t="n">
-        <v>9.780701595329484</v>
+        <v>9.771615081736927</v>
       </c>
       <c r="N2" t="n">
-        <v>150.4809607115913</v>
+        <v>150.3102906665933</v>
       </c>
       <c r="O2" t="n">
-        <v>12.26706813837729</v>
+        <v>12.26010973305677</v>
       </c>
       <c r="P2" t="n">
-        <v>309.0170890068647</v>
+        <v>309.1753813802675</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13461,28 +13541,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6184961892204602</v>
+        <v>0.6012100625080197</v>
       </c>
       <c r="J3" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K3" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2504037177783959</v>
+        <v>0.2389024854324344</v>
       </c>
       <c r="M3" t="n">
-        <v>5.683371880979616</v>
+        <v>5.730790934634366</v>
       </c>
       <c r="N3" t="n">
-        <v>60.05334370735839</v>
+        <v>60.81833773711786</v>
       </c>
       <c r="O3" t="n">
-        <v>7.749409248927198</v>
+        <v>7.798611269778604</v>
       </c>
       <c r="P3" t="n">
-        <v>322.7126715391405</v>
+        <v>322.9022762505546</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13539,28 +13619,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5389832783312344</v>
+        <v>0.5321723387135455</v>
       </c>
       <c r="J4" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K4" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2804896836583372</v>
+        <v>0.2771844965873965</v>
       </c>
       <c r="M4" t="n">
-        <v>4.488148785241587</v>
+        <v>4.499009359744881</v>
       </c>
       <c r="N4" t="n">
-        <v>39.07933832334271</v>
+        <v>39.0054727481067</v>
       </c>
       <c r="O4" t="n">
-        <v>6.25134692073178</v>
+        <v>6.245436153552985</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3095843756085</v>
+        <v>351.3842910927322</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13617,28 +13697,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.419900745355744</v>
+        <v>0.417155449424867</v>
       </c>
       <c r="J5" t="n">
+        <v>310</v>
+      </c>
+      <c r="K5" t="n">
         <v>308</v>
       </c>
-      <c r="K5" t="n">
-        <v>306</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1937941417333122</v>
+        <v>0.1937396160737649</v>
       </c>
       <c r="M5" t="n">
-        <v>4.884318455436333</v>
+        <v>4.866607983704569</v>
       </c>
       <c r="N5" t="n">
-        <v>38.41504517277978</v>
+        <v>38.19687013974116</v>
       </c>
       <c r="O5" t="n">
-        <v>6.19798718720681</v>
+        <v>6.180361651209512</v>
       </c>
       <c r="P5" t="n">
-        <v>361.9524145011451</v>
+        <v>361.9825779974274</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13695,28 +13775,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1691149759864079</v>
+        <v>0.1710209542302556</v>
       </c>
       <c r="J6" t="n">
+        <v>310</v>
+      </c>
+      <c r="K6" t="n">
         <v>308</v>
       </c>
-      <c r="K6" t="n">
-        <v>306</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08189505062214508</v>
+        <v>0.08457487549221865</v>
       </c>
       <c r="M6" t="n">
-        <v>3.294759847773883</v>
+        <v>3.281556371448976</v>
       </c>
       <c r="N6" t="n">
-        <v>16.79196658925409</v>
+        <v>16.69764258410477</v>
       </c>
       <c r="O6" t="n">
-        <v>4.097800213438192</v>
+        <v>4.086274903148927</v>
       </c>
       <c r="P6" t="n">
-        <v>353.5915377396146</v>
+        <v>353.5705950870549</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13773,28 +13853,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2068028791751728</v>
+        <v>0.2054026606528227</v>
       </c>
       <c r="J7" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K7" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06636299116871802</v>
+        <v>0.06634804426866392</v>
       </c>
       <c r="M7" t="n">
-        <v>4.685078626166417</v>
+        <v>4.660773217366821</v>
       </c>
       <c r="N7" t="n">
-        <v>31.42126012096189</v>
+        <v>31.22596102360976</v>
       </c>
       <c r="O7" t="n">
-        <v>5.60546698509249</v>
+        <v>5.588019418685815</v>
       </c>
       <c r="P7" t="n">
-        <v>359.6288321676293</v>
+        <v>359.6442308590468</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13832,7 +13912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26781,6 +26861,90 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-35.12283641373411,173.9798254139868</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-35.12299774160397,173.98073110433538</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-35.12290654060197,173.98171115588957</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-35.12284774544382,173.98261531872564</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-35.122947422817795,173.9835120447806</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-35.12291281183307,173.9844102161387</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-35.12283641373411,173.9798254139868</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-35.12299107657417,173.98073383602647</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-35.122903958856284,173.98171165992008</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-35.122837108146804,173.9826155708495</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-35.12295328343294,173.9835120646036</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-35.1229074922873,173.98441017466482</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H311"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9754,6 +9754,66 @@
       <c r="H311" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="C312" t="n">
+        <v>327.88</v>
+      </c>
+      <c r="D312" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="E312" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="F312" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="G312" t="n">
+        <v>368.34</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>325.35</v>
+      </c>
+      <c r="C313" t="n">
+        <v>330.47</v>
+      </c>
+      <c r="D313" t="n">
+        <v>365.62</v>
+      </c>
+      <c r="E313" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="F313" t="n">
+        <v>359.57</v>
+      </c>
+      <c r="G313" t="n">
+        <v>369.61</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13291,6 +13351,26 @@
       </c>
       <c r="B352" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -13459,28 +13539,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5200744321937278</v>
+        <v>0.522157275763753</v>
       </c>
       <c r="J2" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08679103866615845</v>
+        <v>0.08850078498658254</v>
       </c>
       <c r="M2" t="n">
-        <v>9.771615081736927</v>
+        <v>9.721767257368271</v>
       </c>
       <c r="N2" t="n">
-        <v>150.3102906665933</v>
+        <v>149.363656210096</v>
       </c>
       <c r="O2" t="n">
-        <v>12.26010973305677</v>
+        <v>12.22144247665127</v>
       </c>
       <c r="P2" t="n">
-        <v>309.1753813802675</v>
+        <v>309.1524167326765</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13541,28 +13621,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6012100625080197</v>
+        <v>0.5888761461303198</v>
       </c>
       <c r="J3" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2389024854324344</v>
+        <v>0.2320790782838765</v>
       </c>
       <c r="M3" t="n">
-        <v>5.730790934634366</v>
+        <v>5.755151425835675</v>
       </c>
       <c r="N3" t="n">
-        <v>60.81833773711786</v>
+        <v>61.03255147953497</v>
       </c>
       <c r="O3" t="n">
-        <v>7.798611269778604</v>
+        <v>7.812333292911598</v>
       </c>
       <c r="P3" t="n">
-        <v>322.9022762505546</v>
+        <v>323.0381932539332</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13619,28 +13699,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5321723387135455</v>
+        <v>0.5310376786335245</v>
       </c>
       <c r="J4" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2771844965873965</v>
+        <v>0.2789846813168892</v>
       </c>
       <c r="M4" t="n">
-        <v>4.499009359744881</v>
+        <v>4.477324893251497</v>
       </c>
       <c r="N4" t="n">
-        <v>39.0054727481067</v>
+        <v>38.76572403356941</v>
       </c>
       <c r="O4" t="n">
-        <v>6.245436153552985</v>
+        <v>6.226212655665513</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3842910927322</v>
+        <v>351.3967833890413</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13697,28 +13777,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.417155449424867</v>
+        <v>0.4222296983667371</v>
       </c>
       <c r="J5" t="n">
+        <v>312</v>
+      </c>
+      <c r="K5" t="n">
         <v>310</v>
       </c>
-      <c r="K5" t="n">
-        <v>308</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1937396160737649</v>
+        <v>0.1992364628297847</v>
       </c>
       <c r="M5" t="n">
-        <v>4.866607983704569</v>
+        <v>4.860315704212436</v>
       </c>
       <c r="N5" t="n">
-        <v>38.19687013974116</v>
+        <v>38.05970087105487</v>
       </c>
       <c r="O5" t="n">
-        <v>6.180361651209512</v>
+        <v>6.169254482597948</v>
       </c>
       <c r="P5" t="n">
-        <v>361.9825779974274</v>
+        <v>361.9265287909388</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13775,28 +13855,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1710209542302556</v>
+        <v>0.1739892039982525</v>
       </c>
       <c r="J6" t="n">
+        <v>312</v>
+      </c>
+      <c r="K6" t="n">
         <v>310</v>
       </c>
-      <c r="K6" t="n">
-        <v>308</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08457487549221865</v>
+        <v>0.08816885020976151</v>
       </c>
       <c r="M6" t="n">
-        <v>3.281556371448976</v>
+        <v>3.273436144246345</v>
       </c>
       <c r="N6" t="n">
-        <v>16.69764258410477</v>
+        <v>16.6293854430336</v>
       </c>
       <c r="O6" t="n">
-        <v>4.086274903148927</v>
+        <v>4.077914349644141</v>
       </c>
       <c r="P6" t="n">
-        <v>353.5705950870549</v>
+        <v>353.5378294841628</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13853,28 +13933,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2054026606528227</v>
+        <v>0.2103295715593884</v>
       </c>
       <c r="J7" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K7" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06634804426866392</v>
+        <v>0.07002060311379543</v>
       </c>
       <c r="M7" t="n">
-        <v>4.660773217366821</v>
+        <v>4.658782333499233</v>
       </c>
       <c r="N7" t="n">
-        <v>31.22596102360976</v>
+        <v>31.12205885956955</v>
       </c>
       <c r="O7" t="n">
-        <v>5.588019418685815</v>
+        <v>5.578714803569864</v>
       </c>
       <c r="P7" t="n">
-        <v>359.6442308590468</v>
+        <v>359.5897682091119</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13912,7 +13992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H311"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26945,6 +27025,90 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-35.12273528870001,173.97987285465032</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-35.1229750121432,173.9807404201006</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-35.12287511452512,173.9817172911554</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-35.12279780423563,173.98261650242574</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-35.1229343491378,173.9835120005602</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-35.122871157084674,173.98440989137737</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-35.122723426278,173.97987841964576</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-35.12295288082546,173.9807494907093</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-35.122857665485114,173.98172069770334</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-35.122776529641406,173.98261700667322</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-35.122950217880394,173.98351205423464</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-35.12285970653691,173.98440980210333</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9814,6 +9814,66 @@
       <c r="H313" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>325.35</v>
+      </c>
+      <c r="C314" t="n">
+        <v>331.59</v>
+      </c>
+      <c r="D314" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="E314" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="F314" t="n">
+        <v>357.71</v>
+      </c>
+      <c r="G314" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="C315" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="D315" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="E315" t="n">
+        <v>384.58</v>
+      </c>
+      <c r="F315" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="G315" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13371,6 +13431,26 @@
       </c>
       <c r="B354" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -13539,28 +13619,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.522157275763753</v>
+        <v>0.5175266129996966</v>
       </c>
       <c r="J2" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08850078498658254</v>
+        <v>0.08797939803949972</v>
       </c>
       <c r="M2" t="n">
-        <v>9.721767257368271</v>
+        <v>9.692184647654843</v>
       </c>
       <c r="N2" t="n">
-        <v>149.363656210096</v>
+        <v>148.7188413609969</v>
       </c>
       <c r="O2" t="n">
-        <v>12.22144247665127</v>
+        <v>12.19503347108965</v>
       </c>
       <c r="P2" t="n">
-        <v>309.1524167326765</v>
+        <v>309.2037883130932</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13621,28 +13701,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5888761461303198</v>
+        <v>0.5796697346504298</v>
       </c>
       <c r="J3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K3" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2320790782838765</v>
+        <v>0.2278954280958212</v>
       </c>
       <c r="M3" t="n">
-        <v>5.755151425835675</v>
+        <v>5.763586898327852</v>
       </c>
       <c r="N3" t="n">
-        <v>61.03255147953497</v>
+        <v>60.97877820451757</v>
       </c>
       <c r="O3" t="n">
-        <v>7.812333292911598</v>
+        <v>7.808890971483567</v>
       </c>
       <c r="P3" t="n">
-        <v>323.0381932539332</v>
+        <v>323.1400954295057</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13699,28 +13779,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5310376786335245</v>
+        <v>0.5327380242751736</v>
       </c>
       <c r="J4" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K4" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2789846813168892</v>
+        <v>0.2829261915929582</v>
       </c>
       <c r="M4" t="n">
-        <v>4.477324893251497</v>
+        <v>4.455673047423633</v>
       </c>
       <c r="N4" t="n">
-        <v>38.76572403356941</v>
+        <v>38.52964903427277</v>
       </c>
       <c r="O4" t="n">
-        <v>6.226212655665513</v>
+        <v>6.20722555045914</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3967833890413</v>
+        <v>351.3779602783853</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13777,28 +13857,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4222296983667371</v>
+        <v>0.4351988364901295</v>
       </c>
       <c r="J5" t="n">
+        <v>314</v>
+      </c>
+      <c r="K5" t="n">
         <v>312</v>
       </c>
-      <c r="K5" t="n">
-        <v>310</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1992364628297847</v>
+        <v>0.2083652904931566</v>
       </c>
       <c r="M5" t="n">
-        <v>4.860315704212436</v>
+        <v>4.893979448943658</v>
       </c>
       <c r="N5" t="n">
-        <v>38.05970087105487</v>
+        <v>38.48912231823568</v>
       </c>
       <c r="O5" t="n">
-        <v>6.169254482597948</v>
+        <v>6.203960212496183</v>
       </c>
       <c r="P5" t="n">
-        <v>361.9265287909388</v>
+        <v>361.7826802868951</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13855,28 +13935,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1739892039982525</v>
+        <v>0.1729379584274407</v>
       </c>
       <c r="J6" t="n">
+        <v>314</v>
+      </c>
+      <c r="K6" t="n">
         <v>312</v>
       </c>
-      <c r="K6" t="n">
-        <v>310</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08816885020976151</v>
+        <v>0.08824700259682694</v>
       </c>
       <c r="M6" t="n">
-        <v>3.273436144246345</v>
+        <v>3.258188278364203</v>
       </c>
       <c r="N6" t="n">
-        <v>16.6293854430336</v>
+        <v>16.52802636204385</v>
       </c>
       <c r="O6" t="n">
-        <v>4.077914349644141</v>
+        <v>4.065467545319216</v>
       </c>
       <c r="P6" t="n">
-        <v>353.5378294841628</v>
+        <v>353.549495132302</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13933,28 +14013,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2103295715593884</v>
+        <v>0.2145020588544844</v>
       </c>
       <c r="J7" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K7" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07002060311379543</v>
+        <v>0.07337899087450162</v>
       </c>
       <c r="M7" t="n">
-        <v>4.658782333499233</v>
+        <v>4.652363092745495</v>
       </c>
       <c r="N7" t="n">
-        <v>31.12205885956955</v>
+        <v>30.99275721909326</v>
       </c>
       <c r="O7" t="n">
-        <v>5.578714803569864</v>
+        <v>5.567113903908673</v>
       </c>
       <c r="P7" t="n">
-        <v>359.5897682091119</v>
+        <v>359.5434630814227</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -13992,7 +14072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27109,6 +27189,90 @@
         </is>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-35.122723426278,173.97987841964576</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-35.1229433105257,173.9807534131332</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-35.12284769460507,173.98172264430156</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-35.12273902866158,173.98261789551597</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-35.12296698825607,173.98351211095888</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-35.122866468671425,173.9844098548242</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-35.1228231210934,173.9798316499541</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-35.12294604489707,173.9807522924407</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-35.12284448967933,173.98172326999375</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-35.12271937670571,173.98261836130357</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-35.12297357017768,173.98351213322164</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-35.12287268983516,173.98440990332745</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9863,7 +9863,7 @@
         <v>367.1</v>
       </c>
       <c r="E315" t="n">
-        <v>384.58</v>
+        <v>381.61</v>
       </c>
       <c r="F315" t="n">
         <v>356.98</v>
@@ -9872,6 +9872,66 @@
         <v>368.17</v>
       </c>
       <c r="H315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>303.17</v>
+      </c>
+      <c r="C316" t="n">
+        <v>334.08</v>
+      </c>
+      <c r="D316" t="n">
+        <v>368.51</v>
+      </c>
+      <c r="E316" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="F316" t="n">
+        <v>357.22</v>
+      </c>
+      <c r="G316" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="C317" t="n">
+        <v>332.28</v>
+      </c>
+      <c r="D317" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="E317" t="n">
+        <v>383.68</v>
+      </c>
+      <c r="F317" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="G317" t="n">
+        <v>368.97</v>
+      </c>
+      <c r="H317" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9888,7 +9948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13451,6 +13511,26 @@
       </c>
       <c r="B356" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -13619,28 +13699,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5175266129996966</v>
+        <v>0.4810785305033348</v>
       </c>
       <c r="J2" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K2" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08797939803949972</v>
+        <v>0.07513661328053411</v>
       </c>
       <c r="M2" t="n">
-        <v>9.692184647654843</v>
+        <v>9.773087267034301</v>
       </c>
       <c r="N2" t="n">
-        <v>148.7188413609969</v>
+        <v>153.661320900864</v>
       </c>
       <c r="O2" t="n">
-        <v>12.19503347108965</v>
+        <v>12.39602036545859</v>
       </c>
       <c r="P2" t="n">
-        <v>309.2037883130932</v>
+        <v>309.6091715943857</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13701,28 +13781,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5796697346504298</v>
+        <v>0.572828576605702</v>
       </c>
       <c r="J3" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K3" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2278954280958212</v>
+        <v>0.2255147847102401</v>
       </c>
       <c r="M3" t="n">
-        <v>5.763586898327852</v>
+        <v>5.760041581451075</v>
       </c>
       <c r="N3" t="n">
-        <v>60.97877820451757</v>
+        <v>60.78467548291142</v>
       </c>
       <c r="O3" t="n">
-        <v>7.808890971483567</v>
+        <v>7.796452749995438</v>
       </c>
       <c r="P3" t="n">
-        <v>323.1400954295057</v>
+        <v>323.2161786481907</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13779,28 +13859,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5327380242751736</v>
+        <v>0.5362704079193477</v>
       </c>
       <c r="J4" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K4" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2829261915929582</v>
+        <v>0.2880779208620753</v>
       </c>
       <c r="M4" t="n">
-        <v>4.455673047423633</v>
+        <v>4.441758735621075</v>
       </c>
       <c r="N4" t="n">
-        <v>38.52964903427277</v>
+        <v>38.33511698982946</v>
       </c>
       <c r="O4" t="n">
-        <v>6.20722555045914</v>
+        <v>6.191535915249903</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3779602783853</v>
+        <v>351.3386784807226</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13857,28 +13937,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4351988364901295</v>
+        <v>0.4456819354602722</v>
       </c>
       <c r="J5" t="n">
+        <v>316</v>
+      </c>
+      <c r="K5" t="n">
         <v>314</v>
       </c>
-      <c r="K5" t="n">
-        <v>312</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.2083652904931566</v>
+        <v>0.2166916004766608</v>
       </c>
       <c r="M5" t="n">
-        <v>4.893979448943658</v>
+        <v>4.915800959005391</v>
       </c>
       <c r="N5" t="n">
-        <v>38.48912231823568</v>
+        <v>38.67414503442641</v>
       </c>
       <c r="O5" t="n">
-        <v>6.203960212496183</v>
+        <v>6.218853996873251</v>
       </c>
       <c r="P5" t="n">
-        <v>361.7826802868951</v>
+        <v>361.6658018707203</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13935,28 +14015,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1729379584274407</v>
+        <v>0.1718886834172136</v>
       </c>
       <c r="J6" t="n">
+        <v>316</v>
+      </c>
+      <c r="K6" t="n">
         <v>314</v>
       </c>
-      <c r="K6" t="n">
-        <v>312</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08824700259682694</v>
+        <v>0.08831863945478169</v>
       </c>
       <c r="M6" t="n">
-        <v>3.258188278364203</v>
+        <v>3.243335745110804</v>
       </c>
       <c r="N6" t="n">
-        <v>16.52802636204385</v>
+        <v>16.42726367615209</v>
       </c>
       <c r="O6" t="n">
-        <v>4.065467545319216</v>
+        <v>4.053056090921034</v>
       </c>
       <c r="P6" t="n">
-        <v>353.549495132302</v>
+        <v>353.5611858157323</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14013,28 +14093,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2145020588544844</v>
+        <v>0.2189406561497302</v>
       </c>
       <c r="J7" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K7" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07337899087450162</v>
+        <v>0.07697697139775328</v>
       </c>
       <c r="M7" t="n">
-        <v>4.652363092745495</v>
+        <v>4.647247168187087</v>
       </c>
       <c r="N7" t="n">
-        <v>30.99275721909326</v>
+        <v>30.87479766748213</v>
       </c>
       <c r="O7" t="n">
-        <v>5.567113903908673</v>
+        <v>5.556509485952681</v>
       </c>
       <c r="P7" t="n">
-        <v>359.5434630814227</v>
+        <v>359.4939643860989</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14072,7 +14152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27254,7 +27334,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>-35.12271937670571,173.98261836130357</t>
+          <t>-35.122746150241895,173.98261772672134</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -27268,6 +27348,90 @@
         </is>
       </c>
       <c r="H315" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-35.1229100280361,173.9797908793218</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-35.12292203369806,173.9807621335188</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-35.12283193705347,173.98172572062106</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-35.12273398045274,173.98261801516782</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-35.122971406258245,173.98351212590237</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-35.122867730936534,173.98440986466545</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.123067520544474,173.97971699466868</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.12293741453738,173.98075582962602</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-35.12283229315633,173.9817256510997</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-35.12272748989851,173.98261816900595</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-35.12296915217551,173.98351211827816</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-35.1228654768917,173.9844098470918</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0058/nzd0058.xlsx
+++ b/data/nzd0058/nzd0058.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +9932,96 @@
         <v>368.97</v>
       </c>
       <c r="H317" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>281.63</v>
+      </c>
+      <c r="C318" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="D318" t="n">
+        <v>366.67</v>
+      </c>
+      <c r="E318" t="n">
+        <v>381.74</v>
+      </c>
+      <c r="F318" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="G318" t="n">
+        <v>366.44</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>286.52</v>
+      </c>
+      <c r="C319" t="n">
+        <v>332.61</v>
+      </c>
+      <c r="D319" t="n">
+        <v>368.77</v>
+      </c>
+      <c r="E319" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="F319" t="n">
+        <v>357.83</v>
+      </c>
+      <c r="G319" t="n">
+        <v>366.54</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>291.13</v>
+      </c>
+      <c r="C320" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="D320" t="n">
+        <v>368.48</v>
+      </c>
+      <c r="E320" t="n">
+        <v>380.94</v>
+      </c>
+      <c r="F320" t="n">
+        <v>357.37</v>
+      </c>
+      <c r="G320" t="n">
+        <v>365.58</v>
+      </c>
+      <c r="H320" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9948,7 +10038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13531,6 +13621,36 @@
       </c>
       <c r="B358" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
@@ -13699,28 +13819,28 @@
         <v>0.0276</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4810785305033348</v>
+        <v>0.4151083938237832</v>
       </c>
       <c r="J2" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07513661328053411</v>
+        <v>0.0540602663570936</v>
       </c>
       <c r="M2" t="n">
-        <v>9.773087267034301</v>
+        <v>9.940587419965507</v>
       </c>
       <c r="N2" t="n">
-        <v>153.661320900864</v>
+        <v>164.3001082794999</v>
       </c>
       <c r="O2" t="n">
-        <v>12.39602036545859</v>
+        <v>12.81796037907357</v>
       </c>
       <c r="P2" t="n">
-        <v>309.6091715943857</v>
+        <v>310.345152180246</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -13781,28 +13901,28 @@
         <v>0.1105</v>
       </c>
       <c r="I3" t="n">
-        <v>0.572828576605702</v>
+        <v>0.5604894577477304</v>
       </c>
       <c r="J3" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2255147847102401</v>
+        <v>0.2201518376633426</v>
       </c>
       <c r="M3" t="n">
-        <v>5.760041581451075</v>
+        <v>5.767210358955697</v>
       </c>
       <c r="N3" t="n">
-        <v>60.78467548291142</v>
+        <v>60.63901903058949</v>
       </c>
       <c r="O3" t="n">
-        <v>7.796452749995438</v>
+        <v>7.787105947050515</v>
       </c>
       <c r="P3" t="n">
-        <v>323.2161786481907</v>
+        <v>323.3538348573477</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13859,28 +13979,28 @@
         <v>0.1037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5362704079193477</v>
+        <v>0.5403315037749657</v>
       </c>
       <c r="J4" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2880779208620753</v>
+        <v>0.2949657092869946</v>
       </c>
       <c r="M4" t="n">
-        <v>4.441758735621075</v>
+        <v>4.416829043421478</v>
       </c>
       <c r="N4" t="n">
-        <v>38.33511698982946</v>
+        <v>38.0267159706372</v>
       </c>
       <c r="O4" t="n">
-        <v>6.191535915249903</v>
+        <v>6.166580573594834</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3386784807226</v>
+        <v>351.2933563115444</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13937,28 +14057,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4456819354602722</v>
+        <v>0.4594300376316398</v>
       </c>
       <c r="J5" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2166916004766608</v>
+        <v>0.2282667043632053</v>
       </c>
       <c r="M5" t="n">
-        <v>4.915800959005391</v>
+        <v>4.939600428172584</v>
       </c>
       <c r="N5" t="n">
-        <v>38.67414503442641</v>
+        <v>38.82820751147641</v>
       </c>
       <c r="O5" t="n">
-        <v>6.218853996873251</v>
+        <v>6.231228411114169</v>
       </c>
       <c r="P5" t="n">
-        <v>361.6658018707203</v>
+        <v>361.5121135409891</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14015,28 +14135,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1718886834172136</v>
+        <v>0.1700167311362028</v>
       </c>
       <c r="J6" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K6" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08831863945478169</v>
+        <v>0.08807048996619449</v>
       </c>
       <c r="M6" t="n">
-        <v>3.243335745110804</v>
+        <v>3.223191054477369</v>
       </c>
       <c r="N6" t="n">
-        <v>16.42726367615209</v>
+        <v>16.28538693322147</v>
       </c>
       <c r="O6" t="n">
-        <v>4.053056090921034</v>
+        <v>4.035515696069273</v>
       </c>
       <c r="P6" t="n">
-        <v>353.5611858157323</v>
+        <v>353.582105783886</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14093,28 +14213,28 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2189406561497302</v>
+        <v>0.2204227091653198</v>
       </c>
       <c r="J7" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K7" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07697697139775328</v>
+        <v>0.07934816135723144</v>
       </c>
       <c r="M7" t="n">
-        <v>4.647247168187087</v>
+        <v>4.611431696932209</v>
       </c>
       <c r="N7" t="n">
-        <v>30.87479766748213</v>
+        <v>30.59132466595116</v>
       </c>
       <c r="O7" t="n">
-        <v>5.556509485952681</v>
+        <v>5.530942475378962</v>
       </c>
       <c r="P7" t="n">
-        <v>359.4939643860989</v>
+        <v>359.4773883375485</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14152,7 +14272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27437,6 +27557,132 @@
         </is>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.12309124537361,173.97970586458462</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.122953478969194,173.98074924555775</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-35.12284831778508,173.9817225226392</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-35.12274497833627,173.98261775449765</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-35.12297988160936,173.9835121545695</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-35.1228882878254,173.98441002493712</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.12305010550968,173.97972516461996</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.12293459471685,173.98075698533987</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-35.12282962238486,173.9817261725097</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-35.12275372255514,173.9826175472435</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-35.12296590629635,173.98351210729925</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-35.122887386207466,173.98441001790766</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.1230113212998,173.9797433595234</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.1229350219624,173.9807568102317</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-35.122832204130624,173.98172566848004</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-35.122752190063174,173.9826175835664</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-35.122970053808594,173.9835121213278</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-35.122896041739594,173.98441008539055</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
